--- a/Data/Search_data.xlsx
+++ b/Data/Search_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datn\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D07CA6A-E68E-4EAB-830B-17C0FA2E44E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8039969-5806-4C30-A7FD-3E9E7F568774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2788D3C6-25EF-4D4A-9316-40D19310986B}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>!@#$%</t>
   </si>
   <si>
-    <t>Có 123 kết quả tìm kiếm phù hợp</t>
+    <t>CÓ 131 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
   </si>
 </sst>
 </file>

--- a/Data/Search_data.xlsx
+++ b/Data/Search_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8039969-5806-4C30-A7FD-3E9E7F568774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D537FE7-DFEC-451B-83CF-03EBB7E7942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2788D3C6-25EF-4D4A-9316-40D19310986B}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>!@#$%</t>
   </si>
   <si>
-    <t>CÓ 131 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+    <t>CÓ 130 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
   </si>
 </sst>
 </file>

--- a/Data/Search_data.xlsx
+++ b/Data/Search_data.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D537FE7-DFEC-451B-83CF-03EBB7E7942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17433F53-5638-4BF5-8F34-340194A3C026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2788D3C6-25EF-4D4A-9316-40D19310986B}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>!@#$%</t>
   </si>
   <si>
-    <t>CÓ 130 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+    <t>CÓ 128 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
   </si>
 </sst>
 </file>

--- a/Data/Search_data.xlsx
+++ b/Data/Search_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17433F53-5638-4BF5-8F34-340194A3C026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4304DD4-D7DF-4031-A049-98CDA6A65B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2788D3C6-25EF-4D4A-9316-40D19310986B}"/>
   </bookViews>
@@ -55,7 +55,7 @@
     <t>!@#$%</t>
   </si>
   <si>
-    <t>CÓ 128 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
+    <t>CÓ 131 KẾT QUẢ TÌM KIẾM PHÙ HỢP</t>
   </si>
 </sst>
 </file>
